--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wvarn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Desktop/Filament Master xlsx Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61DEDDC2-A954-4A72-9D95-F2AC5D2E781C}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1095" windowWidth="27510" windowHeight="14145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="186">
   <si>
     <t>Filament Inventory — On-Hand Spools (All Brands)</t>
   </si>
@@ -364,9 +364,6 @@
     <t>#5A6D3D</t>
   </si>
   <si>
-    <t>Catalog lists this color as "Oliver Green" (SL-PLA-22) — likely a brand-catalog typo for Olive Green; matched on color/hex</t>
-  </si>
-  <si>
     <t>SL-PLAP2-02</t>
   </si>
   <si>
@@ -376,9 +373,6 @@
     <t>SUNLU PLA+ 2.0</t>
   </si>
   <si>
-    <t>Physical spool + box label confirm "PLA+2.0" — corrects the prior 2026-08-02 fix, which had wrongly reassigned this to the plain "PLA+" line (SL-PLAP-02) based on the ambiguous user-entered SKU. Verified via IMG_0209.JPG / IMG_0210.JPG, 2026-08-04.</t>
-  </si>
-  <si>
     <t>SL-PLAP2-01</t>
   </si>
   <si>
@@ -388,12 +382,6 @@
     <t>Depleted 8/23/2026. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
   </si>
   <si>
-    <t>Mounted 8/23/2026. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
-  </si>
-  <si>
-    <t>Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
-  </si>
-  <si>
     <t>BL-PLAB-IP</t>
   </si>
   <si>
@@ -580,7 +568,34 @@
     <t>Delivered 8/29/2026</t>
   </si>
   <si>
-    <t>Mounted 8/29/2026 Physical spool + box label confirm "PLA+2.0" — corrects the prior 2026-08-02 fix, which had wrongly reassigned this to the plain "PLA+" line (SL-PLAP-02) based on the ambiguous user-entered SKU. Verified via IMG_0209.JPG / IMG_0210.JPG, 2026-08-04.</t>
+    <t>Mounted 9/12/2026. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
+  </si>
+  <si>
+    <t>Depleted 9/12/2026. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
+  </si>
+  <si>
+    <t>Depleted 9/19/2026 Physical spool + box label confirm "PLA+2.0" — corrects the prior 2026-08-02 fix, which had wrongly reassigned this to the plain "PLA+" line (SL-PLAP-02) based on the ambiguous user-entered SKU. Verified via IMG_0209.JPG / IMG_0210.JPG, 2026-08-04.</t>
+  </si>
+  <si>
+    <t>Mounted 9/19/26Physical spool + box label confirm "PLA+2.0" — corrects the prior 2026-08-02 fix, which had wrongly reassigned this to the plain "PLA+" line (SL-PLAP-02) based on the ambiguous user-entered SKU. Verified via IMG_0209.JPG / IMG_0210.JPG, 2026-08-04.</t>
+  </si>
+  <si>
+    <t>Mounted 9/24/2026 Catalog lists this color as "Oliver Green" (SL-PLA-22) — likely a brand-catalog typo for Olive Green; matched on color/hex</t>
+  </si>
+  <si>
+    <t>Mounted 9/14/26</t>
+  </si>
+  <si>
+    <t>Depleted 9/19/26</t>
+  </si>
+  <si>
+    <t>Mounted 9/19/26</t>
+  </si>
+  <si>
+    <t>Mounted 9/20/26</t>
+  </si>
+  <si>
+    <t>Mounted 9/24/2026</t>
   </si>
 </sst>
 </file>
@@ -1183,6 +1198,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1480,7 +1499,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="76" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B1" s="70"/>
       <c r="C1" s="70"/>
@@ -1490,7 +1509,7 @@
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="77" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B3" s="70"/>
       <c r="C3" s="70"/>
@@ -1500,7 +1519,7 @@
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B4" s="73">
         <f>SUM(Inventory!N3:N114)</f>
@@ -1510,7 +1529,7 @@
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B5" s="75">
         <f>SUMPRODUCT(IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114))</f>
@@ -1520,7 +1539,7 @@
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B6" s="73">
         <f>COUNTIF(Inventory!O3:O114,"*REORDER*")</f>
@@ -1530,7 +1549,7 @@
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B7" s="73">
         <f>Config!$B$3</f>
@@ -1540,7 +1559,7 @@
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="77" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -1553,7 +1572,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -1561,7 +1580,7 @@
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B11" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A11,Inventory!N3:N114),0)</f>
@@ -1587,7 +1606,7 @@
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B13" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A13,Inventory!N3:N114),0)</f>
@@ -1600,7 +1619,7 @@
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B14" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A14,Inventory!N3:N114),0)</f>
@@ -1613,7 +1632,7 @@
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B15" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A15,Inventory!N3:N114),0)</f>
@@ -1626,7 +1645,7 @@
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B16" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A16,Inventory!N3:N114),0)</f>
@@ -1639,7 +1658,7 @@
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B17" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A17,Inventory!N3:N114),0)</f>
@@ -1652,7 +1671,7 @@
     </row>
     <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B18" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A18,Inventory!N3:N114),0)</f>
@@ -1678,7 +1697,7 @@
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B20" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A20,Inventory!N3:N114),0)</f>
@@ -1691,7 +1710,7 @@
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B21" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A21,Inventory!N3:N114),0)</f>
@@ -2234,7 +2253,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="X8" s="4"/>
+      <c r="X8" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="Y8" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2680,11 +2701,11 @@
         <v>1000</v>
       </c>
       <c r="V15" s="5">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="W15" s="9">
         <f t="shared" si="0"/>
-        <v>0.123</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="54">
@@ -2728,10 +2749,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R16" s="7" t="s">
         <v>35</v>
@@ -2744,13 +2765,15 @@
         <v>1000</v>
       </c>
       <c r="V16" s="5">
-        <v>1000</v>
+        <v>533</v>
       </c>
       <c r="W16" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X16" s="4"/>
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="Y16" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3888,10 +3911,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R34" s="7" t="s">
         <v>35</v>
@@ -3911,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="Y34" s="54">
         <f t="shared" si="1"/>
@@ -3923,13 +3946,13 @@
         <v>26</v>
       </c>
       <c r="B35" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>30</v>
@@ -3972,14 +3995,14 @@
         <v>1000</v>
       </c>
       <c r="V35" s="5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9">
         <f t="shared" ref="W35:W66" si="2">IF(V35="","",IF(U35="","",V35/U35))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y35" s="54">
         <f t="shared" ref="Y35:Y65" si="3">IF(OR(M35="",N35=""),0,M35*N35)</f>
@@ -3991,13 +4014,13 @@
         <v>26</v>
       </c>
       <c r="B36" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>30</v>
@@ -4024,10 +4047,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R36" s="7" t="s">
         <v>35</v>
@@ -4040,14 +4063,14 @@
         <v>1000</v>
       </c>
       <c r="V36" s="5">
-        <v>1000</v>
+        <v>801</v>
       </c>
       <c r="W36" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="X36" s="4" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="Y36" s="54">
         <f t="shared" si="3"/>
@@ -4059,13 +4082,13 @@
         <v>26</v>
       </c>
       <c r="B37" s="62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>89</v>
@@ -4115,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Y37" s="54">
         <f t="shared" si="3"/>
@@ -4127,13 +4150,13 @@
         <v>26</v>
       </c>
       <c r="B38" s="62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>89</v>
@@ -4183,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Y38" s="54">
         <f t="shared" si="3"/>
@@ -4195,13 +4218,13 @@
         <v>26</v>
       </c>
       <c r="B39" s="62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>89</v>
@@ -4251,7 +4274,7 @@
         <v>0.246</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="Y39" s="54">
         <f t="shared" si="3"/>
@@ -4263,13 +4286,13 @@
         <v>26</v>
       </c>
       <c r="B40" s="62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>89</v>
@@ -4296,10 +4319,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R40" s="7" t="s">
         <v>35</v>
@@ -4319,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="Y40" s="54">
         <f t="shared" si="3"/>
@@ -4331,7 +4354,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="62" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>40</v>
@@ -4340,11 +4363,11 @@
         <v>40</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F41" s="29"/>
       <c r="G41" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>32</v>
@@ -4378,13 +4401,15 @@
         <v>1000</v>
       </c>
       <c r="V41" s="5">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="W41" s="9">
         <f t="shared" si="2"/>
-        <v>0.70699999999999996</v>
-      </c>
-      <c r="X41" s="4"/>
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="X41" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="Y41" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4395,7 +4420,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="62" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>40</v>
@@ -4404,7 +4429,7 @@
         <v>40</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F42" s="22"/>
       <c r="G42" s="7" t="s">
@@ -4506,14 +4531,14 @@
         <v>1000</v>
       </c>
       <c r="V43" s="5">
-        <v>660</v>
+        <v>350</v>
       </c>
       <c r="W43" s="9">
         <f t="shared" si="2"/>
-        <v>0.66</v>
+        <v>0.35</v>
       </c>
       <c r="X43" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="Y43" s="54">
         <f t="shared" si="3"/>
@@ -4572,14 +4597,14 @@
         <v>1000</v>
       </c>
       <c r="V44" s="5">
-        <v>913</v>
+        <v>482</v>
       </c>
       <c r="W44" s="9">
         <f t="shared" si="2"/>
-        <v>0.91300000000000003</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="X44" s="46" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Y44" s="54">
         <f t="shared" si="3"/>
@@ -4591,7 +4616,7 @@
         <v>38</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>78</v>
@@ -4600,11 +4625,11 @@
         <v>78</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F45" s="30"/>
       <c r="G45" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>32</v>
@@ -4655,7 +4680,7 @@
         <v>26</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>28</v>
@@ -4664,11 +4689,11 @@
         <v>29</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F46" s="31"/>
       <c r="G46" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>32</v>
@@ -4719,7 +4744,7 @@
         <v>38</v>
       </c>
       <c r="B47" s="62" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>78</v>
@@ -4732,7 +4757,7 @@
       </c>
       <c r="F47" s="32"/>
       <c r="G47" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>32</v>
@@ -4894,10 +4919,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="R49" s="7" t="s">
         <v>35</v>
@@ -4927,7 +4952,7 @@
         <v>38</v>
       </c>
       <c r="B50" s="62" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>40</v>
@@ -4936,11 +4961,11 @@
         <v>40</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F50" s="29"/>
       <c r="G50" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>32</v>
@@ -4999,7 +5024,7 @@
         <v>38</v>
       </c>
       <c r="B51" s="62" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>40</v>
@@ -5008,11 +5033,11 @@
         <v>40</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>32</v>
@@ -5071,7 +5096,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="62" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>40</v>
@@ -5080,7 +5105,7 @@
         <v>40</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F52" s="22"/>
       <c r="G52" s="7" t="s">
@@ -5143,7 +5168,7 @@
         <v>38</v>
       </c>
       <c r="B53" s="62" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>40</v>
@@ -5152,7 +5177,7 @@
         <v>40</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F53" s="22"/>
       <c r="G53" s="7" t="s">
@@ -5719,7 +5744,7 @@
         <v>38</v>
       </c>
       <c r="B61" s="62" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>40</v>
@@ -5728,11 +5753,11 @@
         <v>40</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F61" s="33"/>
       <c r="G61" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>32</v>
@@ -5791,7 +5816,7 @@
         <v>38</v>
       </c>
       <c r="B62" s="62" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>40</v>
@@ -5800,11 +5825,11 @@
         <v>40</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F62" s="33"/>
       <c r="G62" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>32</v>
@@ -5830,10 +5855,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P62" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R62" s="7" t="s">
         <v>35</v>
@@ -5846,13 +5871,15 @@
         <v>1000</v>
       </c>
       <c r="V62" s="5">
-        <v>1000</v>
+        <v>967</v>
       </c>
       <c r="W62" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="X62" s="4"/>
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="X62" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="Y62" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
@@ -5863,7 +5890,7 @@
         <v>38</v>
       </c>
       <c r="B63" s="62" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>40</v>
@@ -5872,11 +5899,11 @@
         <v>40</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F63" s="34"/>
       <c r="G63" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>32</v>
@@ -5935,7 +5962,7 @@
         <v>38</v>
       </c>
       <c r="B64" s="62" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>40</v>
@@ -5944,11 +5971,11 @@
         <v>40</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F64" s="34"/>
       <c r="G64" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>32</v>
@@ -6007,7 +6034,7 @@
         <v>38</v>
       </c>
       <c r="B65" s="62" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>40</v>
@@ -6070,7 +6097,7 @@
         <v>38</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C66" s="47" t="s">
         <v>40</v>
@@ -6079,11 +6106,11 @@
         <v>40</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F66" s="48"/>
       <c r="G66" s="52" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H66" s="43" t="s">
         <v>32</v>
@@ -6114,11 +6141,14 @@
         <v>1000</v>
       </c>
       <c r="V66" s="49">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="W66" s="9">
         <f t="shared" si="2"/>
-        <v>0.41299999999999998</v>
+        <v>0</v>
+      </c>
+      <c r="X66" t="s">
+        <v>182</v>
       </c>
       <c r="Y66" s="55">
         <f>IF(OR(M65="",N65=""),0,M65*N65)</f>
@@ -6130,7 +6160,7 @@
         <v>26</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C67" s="47" t="s">
         <v>28</v>
@@ -6139,7 +6169,7 @@
         <v>29</v>
       </c>
       <c r="E67" s="47" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F67" s="57"/>
       <c r="G67" s="40" t="s">
@@ -6149,13 +6179,13 @@
         <v>32</v>
       </c>
       <c r="I67" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J67" s="39">
         <v>46251</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L67" s="40">
         <v>14.99</v>
@@ -6202,7 +6232,7 @@
         <v>26</v>
       </c>
       <c r="B68" s="65" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C68" s="47" t="s">
         <v>28</v>
@@ -6211,7 +6241,7 @@
         <v>29</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F68" s="57"/>
       <c r="G68" s="40" t="s">
@@ -6221,13 +6251,13 @@
         <v>32</v>
       </c>
       <c r="I68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J68" s="39">
         <v>46251</v>
       </c>
       <c r="K68" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L68" s="40">
         <v>14.99</v>
@@ -6274,29 +6304,29 @@
         <v>26</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="E69" s="47" t="s">
         <v>60</v>
       </c>
       <c r="F69" s="58"/>
       <c r="G69" s="40" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H69" s="43" t="s">
         <v>32</v>
       </c>
       <c r="I69" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N69" s="41">
         <v>1</v>
@@ -6328,7 +6358,7 @@
         <v>0.83899999999999997</v>
       </c>
       <c r="X69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="Y69" s="54">
         <f t="shared" si="5"/>
@@ -6362,7 +6392,7 @@
         <v>46263</v>
       </c>
       <c r="K70" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L70" s="40">
         <v>22.99</v>
@@ -6400,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="X70" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y70" s="54">
         <f t="shared" si="5"/>
@@ -6433,7 +6463,7 @@
         <v>46263</v>
       </c>
       <c r="K71" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L71" s="40">
         <v>22.99</v>
@@ -6471,7 +6501,7 @@
         <v>1</v>
       </c>
       <c r="X71" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y71" s="54">
         <f t="shared" si="5"/>
@@ -6483,7 +6513,7 @@
         <v>38</v>
       </c>
       <c r="B72" s="63" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C72" s="64" t="s">
         <v>78</v>
@@ -6496,7 +6526,7 @@
       </c>
       <c r="F72" s="66"/>
       <c r="G72" s="67" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H72" s="42" t="s">
         <v>32</v>
@@ -6505,7 +6535,7 @@
         <v>46263</v>
       </c>
       <c r="K72" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L72" s="40">
         <v>21.84</v>
@@ -6543,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="X72" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y72" s="54">
         <f t="shared" si="5"/>
@@ -6555,7 +6585,7 @@
         <v>38</v>
       </c>
       <c r="B73" s="65" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C73" s="37" t="s">
         <v>78</v>
@@ -6568,7 +6598,7 @@
       </c>
       <c r="F73" s="66"/>
       <c r="G73" s="40" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H73" s="42" t="s">
         <v>32</v>
@@ -6577,7 +6607,7 @@
         <v>46263</v>
       </c>
       <c r="K73" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L73" s="40">
         <v>21.84</v>
@@ -6615,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="X73" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y73" s="54">
         <f t="shared" si="5"/>
@@ -7368,17 +7398,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B1" s="70"/>
       <c r="C1" s="70"/>
     </row>
     <row r="2" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>24</v>
@@ -7386,46 +7416,46 @@
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Desktop/Filament Master xlsx Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61DEDDC2-A954-4A72-9D95-F2AC5D2E781C}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C5813FD-682D-49EF-A8DE-71F673FCB3ED}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4401,11 +4401,11 @@
         <v>1000</v>
       </c>
       <c r="V41" s="5">
-        <v>695</v>
+        <v>138</v>
       </c>
       <c r="W41" s="9">
         <f t="shared" si="2"/>
-        <v>0.69499999999999995</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="X41" s="4" t="s">
         <v>184</v>

--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Desktop/Filament Master xlsx Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C5813FD-682D-49EF-A8DE-71F673FCB3ED}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDEF7FB9-3C38-4262-8558-4BF54448545B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="186">
   <si>
     <t>Filament Inventory — On-Hand Spools (All Brands)</t>
   </si>
@@ -940,7 +940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1166,6 +1166,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1523,7 +1529,7 @@
       </c>
       <c r="B4" s="73">
         <f>SUM(Inventory!N3:N114)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C4" s="74"/>
     </row>
@@ -1543,7 +1549,7 @@
       </c>
       <c r="B6" s="73">
         <f>COUNTIF(Inventory!O3:O114,"*REORDER*")</f>
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="74"/>
     </row>
@@ -1597,7 +1603,7 @@
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A12,Inventory!N3:N114),0)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" s="6">
         <f>IFERROR(SUMPRODUCT((Inventory!A3:A114=A12)*IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114)),0)</f>
@@ -6653,37 +6659,141 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N74" s="41"/>
+      <c r="A74" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F74" s="38"/>
+      <c r="G74" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J74" s="39">
+        <v>46300</v>
+      </c>
+      <c r="K74" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="L74" s="40">
+        <v>23.99</v>
+      </c>
+      <c r="M74" s="40">
+        <v>23.99</v>
+      </c>
+      <c r="N74" s="41">
+        <v>1</v>
+      </c>
       <c r="O74" s="7" t="str">
         <f>IF(OR(N74="",Config!$B$3=""),"",IF(N74&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U74" s="41"/>
-      <c r="V74" s="41"/>
-      <c r="W74" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P74" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q74" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="R74" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="T74" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="U74" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V74" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W74" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y74" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N75" s="41"/>
+      <c r="A75" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D75" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" s="38"/>
+      <c r="G75" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J75" s="39">
+        <v>46300</v>
+      </c>
+      <c r="K75" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="L75" s="40">
+        <v>23.99</v>
+      </c>
+      <c r="M75" s="40">
+        <v>23.99</v>
+      </c>
+      <c r="N75" s="41">
+        <v>1</v>
+      </c>
       <c r="O75" s="7" t="str">
         <f>IF(OR(N75="",Config!$B$3=""),"",IF(N75&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U75" s="41"/>
-      <c r="V75" s="41"/>
-      <c r="W75" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P75" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q75" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="R75" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="T75" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="U75" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V75" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W75" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y75" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">

--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Desktop/Filament Master xlsx Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wvarn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{D4178001-825A-4472-8EAE-C4364B755FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDEF7FB9-3C38-4262-8558-4BF54448545B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A28A61-B2ED-4EA1-AB9E-B85C2E7A903F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="202">
   <si>
     <t>Filament Inventory — On-Hand Spools (All Brands)</t>
   </si>
@@ -596,6 +596,54 @@
   </si>
   <si>
     <t>Mounted 9/24/2026</t>
+  </si>
+  <si>
+    <t>PETG Matte</t>
+  </si>
+  <si>
+    <t>Avocado Green</t>
+  </si>
+  <si>
+    <t>Purchased 10/3/2026</t>
+  </si>
+  <si>
+    <t>BL-PETGM-AVG</t>
+  </si>
+  <si>
+    <t>#999999</t>
+  </si>
+  <si>
+    <t>BL-PETGM-BBL</t>
+  </si>
+  <si>
+    <t>Baby Blue</t>
+  </si>
+  <si>
+    <t>BL-PETGM-BK</t>
+  </si>
+  <si>
+    <t>BL-PETG-GY</t>
+  </si>
+  <si>
+    <t>BL-PETGM-LM</t>
+  </si>
+  <si>
+    <t>Lime</t>
+  </si>
+  <si>
+    <t>BL-PETGM-PK</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>BL-PETGM-VI</t>
+  </si>
+  <si>
+    <t>Violet</t>
+  </si>
+  <si>
+    <t>BL-PETGM-WH</t>
   </si>
 </sst>
 </file>
@@ -606,7 +654,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,8 +750,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -870,6 +924,18 @@
         <fgColor rgb="FFFAE0E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF4FB"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -940,7 +1006,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1168,10 +1234,25 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1202,10 +1283,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1529,7 +1606,7 @@
       </c>
       <c r="B4" s="73">
         <f>SUM(Inventory!N3:N114)</f>
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C4" s="74"/>
     </row>
@@ -1549,7 +1626,7 @@
       </c>
       <c r="B6" s="73">
         <f>COUNTIF(Inventory!O3:O114,"*REORDER*")</f>
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C6" s="74"/>
     </row>
@@ -1603,7 +1680,7 @@
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A12,Inventory!N3:N114),0)</f>
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C12" s="6">
         <f>IFERROR(SUMPRODUCT((Inventory!A3:A114=A12)*IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114)),0)</f>
@@ -6659,7 +6736,7 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="79" t="s">
+      <c r="A74" s="37" t="s">
         <v>38</v>
       </c>
       <c r="B74" s="62" t="s">
@@ -6700,16 +6777,16 @@
         <f>IF(OR(N74="",Config!$B$3=""),"",IF(N74&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P74" s="80" t="s">
+      <c r="P74" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q74" s="80" t="s">
+      <c r="Q74" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R74" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="T74" s="80" t="s">
+      <c r="R74" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T74" s="42" t="s">
         <v>45</v>
       </c>
       <c r="U74" s="41">
@@ -6728,7 +6805,7 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A75" s="79" t="s">
+      <c r="A75" s="37" t="s">
         <v>38</v>
       </c>
       <c r="B75" s="62" t="s">
@@ -6769,16 +6846,16 @@
         <f>IF(OR(N75="",Config!$B$3=""),"",IF(N75&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P75" s="80" t="s">
+      <c r="P75" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q75" s="80" t="s">
+      <c r="Q75" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R75" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="T75" s="80" t="s">
+      <c r="R75" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T75" s="42" t="s">
         <v>45</v>
       </c>
       <c r="U75" s="41">
@@ -6797,261 +6874,1072 @@
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N76" s="41"/>
+      <c r="A76" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" s="84" t="s">
+        <v>189</v>
+      </c>
+      <c r="C76" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D76" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E76" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="G76" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H76" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J76" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K76" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L76" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M76" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N76" s="41">
+        <v>1</v>
+      </c>
       <c r="O76" s="7" t="str">
         <f>IF(OR(N76="",Config!$B$3=""),"",IF(N76&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U76" s="41"/>
-      <c r="V76" s="41"/>
-      <c r="W76" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P76" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q76" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R76" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T76" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U76" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V76" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W76" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X76" t="s">
+        <v>188</v>
       </c>
       <c r="Y76" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N77" s="41"/>
+      <c r="A77" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="C77" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D77" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E77" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="G77" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H77" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J77" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K77" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L77" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M77" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N77" s="41">
+        <v>1</v>
+      </c>
       <c r="O77" s="7" t="str">
         <f>IF(OR(N77="",Config!$B$3=""),"",IF(N77&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U77" s="41"/>
-      <c r="V77" s="41"/>
-      <c r="W77" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P77" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q77" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R77" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T77" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U77" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V77" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W77" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X77" t="s">
+        <v>188</v>
       </c>
       <c r="Y77" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N78" s="41"/>
+      <c r="A78" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="85" t="s">
+        <v>191</v>
+      </c>
+      <c r="C78" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="D78" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E78" s="79" t="s">
+        <v>192</v>
+      </c>
+      <c r="G78" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H78" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J78" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K78" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L78" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M78" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N78" s="41">
+        <v>1</v>
+      </c>
       <c r="O78" s="7" t="str">
         <f>IF(OR(N78="",Config!$B$3=""),"",IF(N78&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U78" s="41"/>
-      <c r="V78" s="41"/>
-      <c r="W78" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P78" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q78" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R78" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T78" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U78" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V78" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W78" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X78" t="s">
+        <v>188</v>
       </c>
       <c r="Y78" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N79" s="41"/>
+      <c r="A79" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="C79" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D79" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="79" t="s">
+        <v>192</v>
+      </c>
+      <c r="G79" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H79" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J79" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K79" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L79" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M79" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N79" s="41">
+        <v>1</v>
+      </c>
       <c r="O79" s="7" t="str">
         <f>IF(OR(N79="",Config!$B$3=""),"",IF(N79&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U79" s="41"/>
-      <c r="V79" s="41"/>
-      <c r="W79" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P79" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q79" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R79" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T79" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U79" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V79" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W79" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X79" t="s">
+        <v>188</v>
       </c>
       <c r="Y79" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N80" s="41"/>
+      <c r="A80" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C80" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D80" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E80" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="G80" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H80" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J80" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K80" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L80" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M80" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N80" s="41">
+        <v>1</v>
+      </c>
       <c r="O80" s="7" t="str">
         <f>IF(OR(N80="",Config!$B$3=""),"",IF(N80&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U80" s="41"/>
-      <c r="V80" s="41"/>
-      <c r="W80" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P80" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q80" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R80" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T80" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U80" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V80" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W80" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X80" t="s">
+        <v>188</v>
       </c>
       <c r="Y80" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N81" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A81" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C81" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D81" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="G81" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H81" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J81" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K81" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M81" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N81" s="41">
+        <v>1</v>
+      </c>
       <c r="O81" s="7" t="str">
         <f>IF(OR(N81="",Config!$B$3=""),"",IF(N81&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U81" s="41"/>
-      <c r="V81" s="41"/>
-      <c r="W81" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P81" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q81" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R81" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T81" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U81" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V81" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W81" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X81" t="s">
+        <v>188</v>
       </c>
       <c r="Y81" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N82" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A82" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="C82" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D82" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E82" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="G82" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H82" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J82" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K82" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L82" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M82" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N82" s="41">
+        <v>1</v>
+      </c>
       <c r="O82" s="7" t="str">
         <f>IF(OR(N82="",Config!$B$3=""),"",IF(N82&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U82" s="41"/>
-      <c r="V82" s="41"/>
-      <c r="W82" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P82" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q82" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R82" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T82" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U82" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V82" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W82" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X82" t="s">
+        <v>188</v>
       </c>
       <c r="Y82" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N83" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A83" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C83" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D83" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="G83" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H83" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J83" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K83" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L83" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M83" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N83" s="41">
+        <v>1</v>
+      </c>
       <c r="O83" s="7" t="str">
         <f>IF(OR(N83="",Config!$B$3=""),"",IF(N83&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U83" s="41"/>
-      <c r="V83" s="41"/>
-      <c r="W83" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P83" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q83" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R83" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T83" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U83" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V83" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W83" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X83" t="s">
+        <v>188</v>
       </c>
       <c r="Y83" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N84" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A84" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D84" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="G84" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H84" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J84" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K84" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L84" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M84" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N84" s="41">
+        <v>1</v>
+      </c>
       <c r="O84" s="7" t="str">
         <f>IF(OR(N84="",Config!$B$3=""),"",IF(N84&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U84" s="41"/>
-      <c r="V84" s="41"/>
-      <c r="W84" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P84" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q84" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R84" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T84" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U84" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V84" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W84" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X84" t="s">
+        <v>188</v>
       </c>
       <c r="Y84" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N85" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A85" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B85" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="C85" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D85" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="G85" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H85" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J85" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K85" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L85" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M85" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N85" s="41">
+        <v>1</v>
+      </c>
       <c r="O85" s="7" t="str">
         <f>IF(OR(N85="",Config!$B$3=""),"",IF(N85&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U85" s="41"/>
-      <c r="V85" s="41"/>
-      <c r="W85" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P85" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q85" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R85" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T85" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U85" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V85" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W85" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X85" t="s">
+        <v>188</v>
       </c>
       <c r="Y85" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N86" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A86" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B86" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="C86" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D86" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E86" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H86" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J86" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K86" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L86" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M86" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N86" s="41">
+        <v>1</v>
+      </c>
       <c r="O86" s="7" t="str">
         <f>IF(OR(N86="",Config!$B$3=""),"",IF(N86&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U86" s="41"/>
-      <c r="V86" s="41"/>
-      <c r="W86" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P86" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q86" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R86" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T86" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U86" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V86" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W86" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X86" t="s">
+        <v>188</v>
       </c>
       <c r="Y86" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N87" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A87" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B87" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="C87" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D87" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E87" s="79" t="s">
+        <v>200</v>
+      </c>
+      <c r="G87" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H87" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J87" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K87" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L87" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M87" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N87" s="41">
+        <v>1</v>
+      </c>
       <c r="O87" s="7" t="str">
         <f>IF(OR(N87="",Config!$B$3=""),"",IF(N87&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U87" s="41"/>
-      <c r="V87" s="41"/>
-      <c r="W87" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P87" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q87" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R87" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T87" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U87" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V87" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W87" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X87" t="s">
+        <v>188</v>
       </c>
       <c r="Y87" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N88" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A88" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B88" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E88" s="79" t="s">
+        <v>200</v>
+      </c>
+      <c r="G88" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H88" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J88" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K88" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M88" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N88" s="41">
+        <v>1</v>
+      </c>
       <c r="O88" s="7" t="str">
         <f>IF(OR(N88="",Config!$B$3=""),"",IF(N88&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U88" s="41"/>
-      <c r="V88" s="41"/>
-      <c r="W88" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P88" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q88" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R88" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T88" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U88" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V88" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W88" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X88" t="s">
+        <v>188</v>
       </c>
       <c r="Y88" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N89" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A89" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B89" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="C89" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D89" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H89" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J89" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K89" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L89" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M89" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N89" s="41">
+        <v>1</v>
+      </c>
       <c r="O89" s="7" t="str">
         <f>IF(OR(N89="",Config!$B$3=""),"",IF(N89&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U89" s="41"/>
-      <c r="V89" s="41"/>
-      <c r="W89" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P89" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q89" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R89" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T89" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U89" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V89" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W89" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X89" t="s">
+        <v>188</v>
       </c>
       <c r="Y89" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N90" s="41"/>
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A90" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B90" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="C90" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D90" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E90" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="G90" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="H90" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="J90" s="39">
+        <v>46302</v>
+      </c>
+      <c r="K90" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="L90" s="40">
+        <v>23.79</v>
+      </c>
+      <c r="M90" s="40">
+        <v>10.19</v>
+      </c>
+      <c r="N90" s="41">
+        <v>1</v>
+      </c>
       <c r="O90" s="7" t="str">
         <f>IF(OR(N90="",Config!$B$3=""),"",IF(N90&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U90" s="41"/>
-      <c r="V90" s="41"/>
-      <c r="W90" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P90" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q90" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="R90" s="82" t="s">
+        <v>35</v>
+      </c>
+      <c r="T90" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U90" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V90" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W90" s="9">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="X90" t="s">
+        <v>188</v>
       </c>
       <c r="Y90" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="14:25" x14ac:dyDescent="0.25">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A91" s="37"/>
       <c r="N91" s="41"/>
       <c r="O91" s="7" t="str">
         <f>IF(OR(N91="",Config!$B$3=""),"",IF(N91&lt;=Config!$B$3,"⚠ REORDER",""))</f>
@@ -7068,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="14:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N92" s="41"/>
       <c r="O92" s="7" t="str">
         <f>IF(OR(N92="",Config!$B$3=""),"",IF(N92&lt;=Config!$B$3,"⚠ REORDER",""))</f>
@@ -7085,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="14:25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N93" s="41"/>
       <c r="O93" s="7" t="str">
         <f>IF(OR(N93="",Config!$B$3=""),"",IF(N93&lt;=Config!$B$3,"⚠ REORDER",""))</f>
@@ -7102,7 +7990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="14:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N94" s="41"/>
       <c r="O94" s="7" t="str">
         <f>IF(OR(N94="",Config!$B$3=""),"",IF(N94&lt;=Config!$B$3,"⚠ REORDER",""))</f>
@@ -7119,7 +8007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="14:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N95" s="41"/>
       <c r="O95" s="7" t="str">
         <f>IF(OR(N95="",Config!$B$3=""),"",IF(N95&lt;=Config!$B$3,"⚠ REORDER",""))</f>
@@ -7136,7 +8024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="14:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N96" s="41"/>
       <c r="O96" s="7" t="str">
         <f>IF(OR(N96="",Config!$B$3=""),"",IF(N96&lt;=Config!$B$3,"⚠ REORDER",""))</f>
@@ -7470,7 +8358,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="A3:A64 A66:A71 A73:A114" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A3:A64 A66:A71 A73:A77 A79:A114" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"AzureFilm,Bambu Lab,Creality Hyper,Hatchbox,MatterHackers,Overture,Polymaker,Prusament,SUNLU,VoxelPLA,eSUN"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="P3:P114" xr:uid="{00000000-0002-0000-0100-000001000000}">

--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wvarn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A28A61-B2ED-4EA1-AB9E-B85C2E7A903F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9959AA4D-8ED7-4924-B8CF-609ACEB252E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="203">
   <si>
     <t>Filament Inventory — On-Hand Spools (All Brands)</t>
   </si>
@@ -644,6 +644,9 @@
   </si>
   <si>
     <t>BL-PETGM-WH</t>
+  </si>
+  <si>
+    <t>Mounted 10/8/2026</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1205,6 +1208,15 @@
     <xf numFmtId="0" fontId="15" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1232,27 +1244,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1581,74 +1572,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="73">
+      <c r="B4" s="76">
         <f>SUM(Inventory!N3:N114)</f>
         <v>87</v>
       </c>
-      <c r="C4" s="74"/>
+      <c r="C4" s="77"/>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="78">
         <f>SUMPRODUCT(IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="74"/>
+      <c r="C5" s="77"/>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="73">
+      <c r="B6" s="76">
         <f>COUNTIF(Inventory!O3:O114,"*REORDER*")</f>
         <v>88</v>
       </c>
-      <c r="C6" s="74"/>
+      <c r="C6" s="77"/>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="73">
+      <c r="B7" s="76">
         <f>Config!$B$3</f>
         <v>1</v>
       </c>
-      <c r="C7" s="74"/>
+      <c r="C7" s="77"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -1851,33 +1842,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="69"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="72"/>
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="75"/>
     </row>
     <row r="2" spans="1:25" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2074,11 +2065,11 @@
         <v>1000</v>
       </c>
       <c r="V4" s="5">
-        <v>483</v>
+        <v>114</v>
       </c>
       <c r="W4" s="9">
         <f t="shared" si="0"/>
-        <v>0.48299999999999998</v>
+        <v>0.114</v>
       </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="54">
@@ -2314,10 +2305,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R8" s="7" t="s">
         <v>35</v>
@@ -2330,11 +2321,11 @@
         <v>1000</v>
       </c>
       <c r="V8" s="5">
-        <v>1000</v>
+        <v>9647</v>
       </c>
       <c r="W8" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>9.6470000000000002</v>
       </c>
       <c r="X8" s="4" t="s">
         <v>185</v>
@@ -2460,11 +2451,11 @@
         <v>1000</v>
       </c>
       <c r="V10" s="5">
-        <v>939</v>
+        <v>861</v>
       </c>
       <c r="W10" s="9">
         <f t="shared" si="0"/>
-        <v>0.93899999999999995</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="X10" s="4"/>
       <c r="Y10" s="54">
@@ -3562,11 +3553,11 @@
         <v>1000</v>
       </c>
       <c r="V27" s="5">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="W27" s="9">
         <f t="shared" si="0"/>
-        <v>0.23300000000000001</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="54">
@@ -6778,10 +6769,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P74" s="42" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="Q74" s="42" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R74" s="42" t="s">
         <v>35</v>
@@ -6798,6 +6789,9 @@
       <c r="W74" s="9">
         <f t="shared" si="4"/>
         <v>1</v>
+      </c>
+      <c r="X74" t="s">
+        <v>202</v>
       </c>
       <c r="Y74" s="54">
         <f t="shared" si="5"/>
@@ -6877,22 +6871,22 @@
       <c r="A76" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="B76" s="84" t="s">
+      <c r="B76" s="69" t="s">
         <v>189</v>
       </c>
-      <c r="C76" s="79" t="s">
+      <c r="C76" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D76" s="80" t="s">
+      <c r="D76" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E76" s="79" t="s">
+      <c r="E76" s="47" t="s">
         <v>187</v>
       </c>
       <c r="G76" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H76" s="81" t="s">
+      <c r="H76" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J76" s="39">
@@ -6914,16 +6908,16 @@
         <f>IF(OR(N76="",Config!$B$3=""),"",IF(N76&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P76" s="82" t="s">
+      <c r="P76" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q76" s="82" t="s">
+      <c r="Q76" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R76" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T76" s="82" t="s">
+      <c r="R76" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T76" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U76" s="41">
@@ -6951,19 +6945,19 @@
       <c r="B77" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="C77" s="79" t="s">
+      <c r="C77" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D77" s="80" t="s">
+      <c r="D77" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E77" s="79" t="s">
+      <c r="E77" s="47" t="s">
         <v>187</v>
       </c>
       <c r="G77" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H77" s="81" t="s">
+      <c r="H77" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J77" s="39">
@@ -6985,16 +6979,16 @@
         <f>IF(OR(N77="",Config!$B$3=""),"",IF(N77&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P77" s="82" t="s">
+      <c r="P77" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q77" s="82" t="s">
+      <c r="Q77" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R77" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T77" s="82" t="s">
+      <c r="R77" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T77" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U77" s="41">
@@ -7016,25 +7010,25 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A78" s="83" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="85" t="s">
+      <c r="A78" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="70" t="s">
         <v>191</v>
       </c>
-      <c r="C78" s="83" t="s">
+      <c r="C78" s="68" t="s">
         <v>186</v>
       </c>
-      <c r="D78" s="80" t="s">
+      <c r="D78" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E78" s="79" t="s">
+      <c r="E78" s="47" t="s">
         <v>192</v>
       </c>
       <c r="G78" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H78" s="81" t="s">
+      <c r="H78" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J78" s="39">
@@ -7056,16 +7050,16 @@
         <f>IF(OR(N78="",Config!$B$3=""),"",IF(N78&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P78" s="82" t="s">
+      <c r="P78" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q78" s="82" t="s">
+      <c r="Q78" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R78" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T78" s="82" t="s">
+      <c r="R78" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T78" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U78" s="41">
@@ -7093,19 +7087,19 @@
       <c r="B79" s="65" t="s">
         <v>191</v>
       </c>
-      <c r="C79" s="79" t="s">
+      <c r="C79" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D79" s="80" t="s">
+      <c r="D79" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E79" s="79" t="s">
+      <c r="E79" s="47" t="s">
         <v>192</v>
       </c>
       <c r="G79" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H79" s="81" t="s">
+      <c r="H79" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J79" s="39">
@@ -7127,16 +7121,16 @@
         <f>IF(OR(N79="",Config!$B$3=""),"",IF(N79&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P79" s="82" t="s">
+      <c r="P79" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q79" s="82" t="s">
+      <c r="Q79" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R79" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T79" s="82" t="s">
+      <c r="R79" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T79" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U79" s="41">
@@ -7164,19 +7158,19 @@
       <c r="B80" s="65" t="s">
         <v>193</v>
       </c>
-      <c r="C80" s="79" t="s">
+      <c r="C80" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D80" s="80" t="s">
+      <c r="D80" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E80" s="79" t="s">
+      <c r="E80" s="47" t="s">
         <v>89</v>
       </c>
       <c r="G80" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H80" s="81" t="s">
+      <c r="H80" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J80" s="39">
@@ -7198,16 +7192,16 @@
         <f>IF(OR(N80="",Config!$B$3=""),"",IF(N80&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P80" s="82" t="s">
+      <c r="P80" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q80" s="82" t="s">
+      <c r="Q80" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R80" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T80" s="82" t="s">
+      <c r="R80" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T80" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U80" s="41">
@@ -7235,19 +7229,19 @@
       <c r="B81" s="65" t="s">
         <v>193</v>
       </c>
-      <c r="C81" s="79" t="s">
+      <c r="C81" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D81" s="80" t="s">
+      <c r="D81" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E81" s="79" t="s">
+      <c r="E81" s="47" t="s">
         <v>89</v>
       </c>
       <c r="G81" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H81" s="81" t="s">
+      <c r="H81" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J81" s="39">
@@ -7269,16 +7263,16 @@
         <f>IF(OR(N81="",Config!$B$3=""),"",IF(N81&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P81" s="82" t="s">
+      <c r="P81" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q81" s="82" t="s">
+      <c r="Q81" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R81" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T81" s="82" t="s">
+      <c r="R81" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T81" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U81" s="41">
@@ -7306,19 +7300,19 @@
       <c r="B82" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="C82" s="79" t="s">
+      <c r="C82" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D82" s="80" t="s">
+      <c r="D82" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E82" s="79" t="s">
+      <c r="E82" s="47" t="s">
         <v>89</v>
       </c>
       <c r="G82" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H82" s="81" t="s">
+      <c r="H82" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J82" s="39">
@@ -7340,16 +7334,16 @@
         <f>IF(OR(N82="",Config!$B$3=""),"",IF(N82&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P82" s="82" t="s">
+      <c r="P82" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q82" s="82" t="s">
+      <c r="Q82" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R82" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T82" s="82" t="s">
+      <c r="R82" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T82" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U82" s="41">
@@ -7377,19 +7371,19 @@
       <c r="B83" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="C83" s="79" t="s">
+      <c r="C83" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D83" s="80" t="s">
+      <c r="D83" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E83" s="79" t="s">
+      <c r="E83" s="47" t="s">
         <v>196</v>
       </c>
       <c r="G83" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H83" s="81" t="s">
+      <c r="H83" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J83" s="39">
@@ -7411,16 +7405,16 @@
         <f>IF(OR(N83="",Config!$B$3=""),"",IF(N83&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P83" s="82" t="s">
+      <c r="P83" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q83" s="82" t="s">
+      <c r="Q83" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R83" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T83" s="82" t="s">
+      <c r="R83" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T83" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U83" s="41">
@@ -7448,19 +7442,19 @@
       <c r="B84" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="C84" s="79" t="s">
+      <c r="C84" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D84" s="80" t="s">
+      <c r="D84" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E84" s="79" t="s">
+      <c r="E84" s="47" t="s">
         <v>196</v>
       </c>
       <c r="G84" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H84" s="81" t="s">
+      <c r="H84" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J84" s="39">
@@ -7482,16 +7476,16 @@
         <f>IF(OR(N84="",Config!$B$3=""),"",IF(N84&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P84" s="82" t="s">
+      <c r="P84" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q84" s="82" t="s">
+      <c r="Q84" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R84" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T84" s="82" t="s">
+      <c r="R84" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T84" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U84" s="41">
@@ -7519,19 +7513,19 @@
       <c r="B85" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="C85" s="79" t="s">
+      <c r="C85" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D85" s="80" t="s">
+      <c r="D85" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E85" s="79" t="s">
+      <c r="E85" s="47" t="s">
         <v>198</v>
       </c>
       <c r="G85" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H85" s="81" t="s">
+      <c r="H85" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J85" s="39">
@@ -7553,16 +7547,16 @@
         <f>IF(OR(N85="",Config!$B$3=""),"",IF(N85&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P85" s="82" t="s">
+      <c r="P85" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q85" s="82" t="s">
+      <c r="Q85" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R85" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T85" s="82" t="s">
+      <c r="R85" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T85" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U85" s="41">
@@ -7590,19 +7584,19 @@
       <c r="B86" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="C86" s="79" t="s">
+      <c r="C86" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D86" s="80" t="s">
+      <c r="D86" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E86" s="79" t="s">
+      <c r="E86" s="47" t="s">
         <v>198</v>
       </c>
       <c r="G86" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H86" s="81" t="s">
+      <c r="H86" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J86" s="39">
@@ -7624,16 +7618,16 @@
         <f>IF(OR(N86="",Config!$B$3=""),"",IF(N86&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P86" s="82" t="s">
+      <c r="P86" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q86" s="82" t="s">
+      <c r="Q86" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R86" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T86" s="82" t="s">
+      <c r="R86" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T86" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U86" s="41">
@@ -7661,19 +7655,19 @@
       <c r="B87" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="C87" s="79" t="s">
+      <c r="C87" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D87" s="80" t="s">
+      <c r="D87" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E87" s="79" t="s">
+      <c r="E87" s="47" t="s">
         <v>200</v>
       </c>
       <c r="G87" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H87" s="81" t="s">
+      <c r="H87" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J87" s="39">
@@ -7695,16 +7689,16 @@
         <f>IF(OR(N87="",Config!$B$3=""),"",IF(N87&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P87" s="82" t="s">
+      <c r="P87" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q87" s="82" t="s">
+      <c r="Q87" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R87" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T87" s="82" t="s">
+      <c r="R87" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T87" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U87" s="41">
@@ -7732,19 +7726,19 @@
       <c r="B88" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="C88" s="79" t="s">
+      <c r="C88" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D88" s="80" t="s">
+      <c r="D88" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E88" s="79" t="s">
+      <c r="E88" s="47" t="s">
         <v>200</v>
       </c>
       <c r="G88" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H88" s="81" t="s">
+      <c r="H88" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J88" s="39">
@@ -7766,16 +7760,16 @@
         <f>IF(OR(N88="",Config!$B$3=""),"",IF(N88&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P88" s="82" t="s">
+      <c r="P88" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q88" s="82" t="s">
+      <c r="Q88" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R88" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T88" s="82" t="s">
+      <c r="R88" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T88" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U88" s="41">
@@ -7803,19 +7797,19 @@
       <c r="B89" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="C89" s="79" t="s">
+      <c r="C89" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D89" s="80" t="s">
+      <c r="D89" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E89" s="79" t="s">
+      <c r="E89" s="47" t="s">
         <v>30</v>
       </c>
       <c r="G89" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H89" s="81" t="s">
+      <c r="H89" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J89" s="39">
@@ -7837,16 +7831,16 @@
         <f>IF(OR(N89="",Config!$B$3=""),"",IF(N89&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P89" s="82" t="s">
+      <c r="P89" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q89" s="82" t="s">
+      <c r="Q89" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R89" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T89" s="82" t="s">
+      <c r="R89" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T89" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U89" s="41">
@@ -7874,19 +7868,19 @@
       <c r="B90" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="C90" s="79" t="s">
+      <c r="C90" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D90" s="80" t="s">
+      <c r="D90" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="E90" s="79" t="s">
+      <c r="E90" s="47" t="s">
         <v>30</v>
       </c>
       <c r="G90" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="H90" s="81" t="s">
+      <c r="H90" s="43" t="s">
         <v>32</v>
       </c>
       <c r="J90" s="39">
@@ -7908,16 +7902,16 @@
         <f>IF(OR(N90="",Config!$B$3=""),"",IF(N90&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P90" s="82" t="s">
+      <c r="P90" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="Q90" s="82" t="s">
+      <c r="Q90" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="R90" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="T90" s="82" t="s">
+      <c r="R90" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="T90" s="42" t="s">
         <v>36</v>
       </c>
       <c r="U90" s="41">
@@ -8395,11 +8389,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="81" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
     </row>
     <row r="2" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
